--- a/matched_pivot_2.xlsx
+++ b/matched_pivot_2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="19">
   <si>
     <t>subid</t>
   </si>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F760"/>
+  <dimension ref="A1:F761"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -708,7 +708,7 @@
         <v>1027</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
@@ -722,7 +722,7 @@
         <v>1027</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -736,7 +736,7 @@
         <v>1027</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -750,7 +750,7 @@
         <v>1027</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
@@ -764,7 +764,7 @@
         <v>1027</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
@@ -778,7 +778,7 @@
         <v>1027</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
         <v>14</v>
@@ -1156,7 +1156,7 @@
         <v>1039</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -1464,7 +1464,7 @@
         <v>1050</v>
       </c>
       <c r="C74">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -1478,7 +1478,7 @@
         <v>1051</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
@@ -1492,7 +1492,7 @@
         <v>1051</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="s">
         <v>9</v>
@@ -1506,7 +1506,7 @@
         <v>1051</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D77" t="s">
         <v>13</v>
@@ -1898,7 +1898,7 @@
         <v>1062</v>
       </c>
       <c r="C105">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D105" t="s">
         <v>12</v>
@@ -1912,7 +1912,7 @@
         <v>1062</v>
       </c>
       <c r="C106">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D106" t="s">
         <v>13</v>
@@ -2528,7 +2528,7 @@
         <v>1079</v>
       </c>
       <c r="C150">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -2542,7 +2542,7 @@
         <v>1079</v>
       </c>
       <c r="C151">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D151" t="s">
         <v>16</v>
@@ -2556,7 +2556,7 @@
         <v>1079</v>
       </c>
       <c r="C152">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D152" t="s">
         <v>11</v>
@@ -2976,7 +2976,7 @@
         <v>1086</v>
       </c>
       <c r="C182">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D182" t="s">
         <v>10</v>
@@ -2990,7 +2990,7 @@
         <v>1086</v>
       </c>
       <c r="C183">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D183" t="s">
         <v>6</v>
@@ -3133,7 +3133,7 @@
         <v>9</v>
       </c>
       <c r="D193" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3147,7 +3147,7 @@
         <v>10</v>
       </c>
       <c r="D194" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3161,7 +3161,7 @@
         <v>11</v>
       </c>
       <c r="D195" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3175,7 +3175,7 @@
         <v>12</v>
       </c>
       <c r="D196" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3203,7 +3203,7 @@
         <v>14</v>
       </c>
       <c r="D198" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3211,13 +3211,13 @@
         <v>197</v>
       </c>
       <c r="B199">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C199">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D199" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3228,10 +3228,10 @@
         <v>1091</v>
       </c>
       <c r="C200">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D200" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3242,10 +3242,10 @@
         <v>1091</v>
       </c>
       <c r="C201">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D201" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3256,10 +3256,10 @@
         <v>1091</v>
       </c>
       <c r="C202">
+        <v>6</v>
+      </c>
+      <c r="D202" t="s">
         <v>15</v>
-      </c>
-      <c r="D202" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3273,7 +3273,7 @@
         <v>16</v>
       </c>
       <c r="D203" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3284,10 +3284,10 @@
         <v>1091</v>
       </c>
       <c r="C204">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D204" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3295,13 +3295,13 @@
         <v>203</v>
       </c>
       <c r="B205">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D205" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3312,7 +3312,7 @@
         <v>1094</v>
       </c>
       <c r="C206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D206" t="s">
         <v>6</v>
@@ -3326,10 +3326,10 @@
         <v>1094</v>
       </c>
       <c r="C207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3340,10 +3340,10 @@
         <v>1094</v>
       </c>
       <c r="C208">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D208" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -3351,13 +3351,13 @@
         <v>207</v>
       </c>
       <c r="B209">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="C209">
         <v>3</v>
       </c>
       <c r="D209" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -3368,16 +3368,10 @@
         <v>1097</v>
       </c>
       <c r="C210">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D210" t="s">
-        <v>15</v>
-      </c>
-      <c r="E210" t="s">
-        <v>16</v>
-      </c>
-      <c r="F210" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -3388,10 +3382,16 @@
         <v>1097</v>
       </c>
       <c r="C211">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D211" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="E211" t="s">
+        <v>16</v>
+      </c>
+      <c r="F211" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -3402,10 +3402,10 @@
         <v>1097</v>
       </c>
       <c r="C212">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D212" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -3416,13 +3416,10 @@
         <v>1097</v>
       </c>
       <c r="C213">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D213" t="s">
-        <v>14</v>
-      </c>
-      <c r="E213" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -3433,9 +3430,12 @@
         <v>1097</v>
       </c>
       <c r="C214">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D214" t="s">
+        <v>14</v>
+      </c>
+      <c r="E214" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3444,13 +3444,13 @@
         <v>213</v>
       </c>
       <c r="B215">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D215" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -3461,10 +3461,10 @@
         <v>1098</v>
       </c>
       <c r="C216">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D216" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -3475,10 +3475,10 @@
         <v>1098</v>
       </c>
       <c r="C217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D217" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -3486,13 +3486,13 @@
         <v>216</v>
       </c>
       <c r="B218">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="C218">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D218" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -3503,10 +3503,10 @@
         <v>1103</v>
       </c>
       <c r="C219">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D219" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -3517,10 +3517,10 @@
         <v>1103</v>
       </c>
       <c r="C220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D220" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -3531,13 +3531,10 @@
         <v>1103</v>
       </c>
       <c r="C221">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D221" t="s">
-        <v>8</v>
-      </c>
-      <c r="E221" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -3548,10 +3545,13 @@
         <v>1103</v>
       </c>
       <c r="C222">
+        <v>6</v>
+      </c>
+      <c r="D222" t="s">
         <v>8</v>
       </c>
-      <c r="D222" t="s">
-        <v>12</v>
+      <c r="E222" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -3562,10 +3562,10 @@
         <v>1103</v>
       </c>
       <c r="C223">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D223" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -3573,13 +3573,13 @@
         <v>222</v>
       </c>
       <c r="B224">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C224">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D224" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3587,13 +3587,13 @@
         <v>223</v>
       </c>
       <c r="B225">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C225">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -3604,10 +3604,10 @@
         <v>1105</v>
       </c>
       <c r="C226">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D226" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3618,10 +3618,10 @@
         <v>1105</v>
       </c>
       <c r="C227">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D227" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3632,10 +3632,10 @@
         <v>1105</v>
       </c>
       <c r="C228">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D228" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -3646,10 +3646,10 @@
         <v>1105</v>
       </c>
       <c r="C229">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D229" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -3660,10 +3660,10 @@
         <v>1105</v>
       </c>
       <c r="C230">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D230" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3671,13 +3671,13 @@
         <v>229</v>
       </c>
       <c r="B231">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D231" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3688,10 +3688,10 @@
         <v>1106</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3699,13 +3699,13 @@
         <v>231</v>
       </c>
       <c r="B233">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D233" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -3716,10 +3716,10 @@
         <v>1107</v>
       </c>
       <c r="C234">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D234" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -3730,10 +3730,10 @@
         <v>1107</v>
       </c>
       <c r="C235">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D235" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -3741,13 +3741,13 @@
         <v>234</v>
       </c>
       <c r="B236">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C236">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D236" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -3755,13 +3755,13 @@
         <v>235</v>
       </c>
       <c r="B237">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C237">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3772,10 +3772,10 @@
         <v>1109</v>
       </c>
       <c r="C238">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D238" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3786,10 +3786,10 @@
         <v>1109</v>
       </c>
       <c r="C239">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D239" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3797,13 +3797,13 @@
         <v>238</v>
       </c>
       <c r="B240">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D240" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3814,10 +3814,10 @@
         <v>1110</v>
       </c>
       <c r="C241">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D241" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -3828,10 +3828,10 @@
         <v>1110</v>
       </c>
       <c r="C242">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D242" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -3842,10 +3842,10 @@
         <v>1110</v>
       </c>
       <c r="C243">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D243" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3856,10 +3856,10 @@
         <v>1110</v>
       </c>
       <c r="C244">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D244" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -3870,10 +3870,10 @@
         <v>1110</v>
       </c>
       <c r="C245">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D245" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -3881,13 +3881,13 @@
         <v>244</v>
       </c>
       <c r="B246">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C246">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D246" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -3898,10 +3898,10 @@
         <v>1111</v>
       </c>
       <c r="C247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3912,10 +3912,10 @@
         <v>1111</v>
       </c>
       <c r="C248">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D248" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3926,10 +3926,10 @@
         <v>1111</v>
       </c>
       <c r="C249">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D249" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -3940,10 +3940,10 @@
         <v>1111</v>
       </c>
       <c r="C250">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D250" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3954,10 +3954,10 @@
         <v>1111</v>
       </c>
       <c r="C251">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D251" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3965,13 +3965,13 @@
         <v>250</v>
       </c>
       <c r="B252">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C252">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D252" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -3979,13 +3979,13 @@
         <v>251</v>
       </c>
       <c r="B253">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3996,10 +3996,10 @@
         <v>1115</v>
       </c>
       <c r="C254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D254" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4010,10 +4010,10 @@
         <v>1115</v>
       </c>
       <c r="C255">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4024,10 +4024,10 @@
         <v>1115</v>
       </c>
       <c r="C256">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D256" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4038,10 +4038,10 @@
         <v>1115</v>
       </c>
       <c r="C257">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D257" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4049,13 +4049,13 @@
         <v>256</v>
       </c>
       <c r="B258">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D258" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4066,10 +4066,10 @@
         <v>1117</v>
       </c>
       <c r="C259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D259" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4080,10 +4080,10 @@
         <v>1117</v>
       </c>
       <c r="C260">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4094,10 +4094,10 @@
         <v>1117</v>
       </c>
       <c r="C261">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D261" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4108,10 +4108,10 @@
         <v>1117</v>
       </c>
       <c r="C262">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D262" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4122,10 +4122,10 @@
         <v>1117</v>
       </c>
       <c r="C263">
+        <v>7</v>
+      </c>
+      <c r="D263" t="s">
         <v>9</v>
-      </c>
-      <c r="D263" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4133,13 +4133,13 @@
         <v>262</v>
       </c>
       <c r="B264">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C264">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D264" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4150,10 +4150,10 @@
         <v>1118</v>
       </c>
       <c r="C265">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D265" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4164,7 +4164,7 @@
         <v>1118</v>
       </c>
       <c r="C266">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D266" t="s">
         <v>17</v>
@@ -4178,10 +4178,10 @@
         <v>1118</v>
       </c>
       <c r="C267">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D267" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4189,13 +4189,13 @@
         <v>266</v>
       </c>
       <c r="B268">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C268">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D268" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4206,10 +4206,10 @@
         <v>1119</v>
       </c>
       <c r="C269">
+        <v>7</v>
+      </c>
+      <c r="D269" t="s">
         <v>8</v>
-      </c>
-      <c r="D269" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4217,13 +4217,13 @@
         <v>268</v>
       </c>
       <c r="B270">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C270">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D270" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4234,10 +4234,10 @@
         <v>1121</v>
       </c>
       <c r="C271">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D271" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4248,10 +4248,10 @@
         <v>1121</v>
       </c>
       <c r="C272">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D272" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4262,10 +4262,10 @@
         <v>1121</v>
       </c>
       <c r="C273">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D273" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4273,13 +4273,13 @@
         <v>272</v>
       </c>
       <c r="B274">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C274">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D274" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4287,13 +4287,13 @@
         <v>273</v>
       </c>
       <c r="B275">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D275" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4304,10 +4304,10 @@
         <v>1123</v>
       </c>
       <c r="C276">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4318,10 +4318,10 @@
         <v>1123</v>
       </c>
       <c r="C277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D277" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4332,10 +4332,10 @@
         <v>1123</v>
       </c>
       <c r="C278">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D278" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4343,13 +4343,13 @@
         <v>277</v>
       </c>
       <c r="B279">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C279">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D279" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4357,13 +4357,13 @@
         <v>278</v>
       </c>
       <c r="B280">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C280">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D280" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4374,10 +4374,10 @@
         <v>1125</v>
       </c>
       <c r="C281">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D281" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4385,13 +4385,13 @@
         <v>280</v>
       </c>
       <c r="B282">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C282">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D282" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4402,10 +4402,10 @@
         <v>1126</v>
       </c>
       <c r="C283">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D283" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4416,10 +4416,10 @@
         <v>1126</v>
       </c>
       <c r="C284">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4430,10 +4430,10 @@
         <v>1126</v>
       </c>
       <c r="C285">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D285" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4444,10 +4444,10 @@
         <v>1126</v>
       </c>
       <c r="C286">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D286" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4458,10 +4458,10 @@
         <v>1126</v>
       </c>
       <c r="C287">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D287" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4469,13 +4469,13 @@
         <v>286</v>
       </c>
       <c r="B288">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C288">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D288" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4486,10 +4486,10 @@
         <v>1128</v>
       </c>
       <c r="C289">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D289" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -4500,10 +4500,10 @@
         <v>1128</v>
       </c>
       <c r="C290">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D290" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4514,10 +4514,10 @@
         <v>1128</v>
       </c>
       <c r="C291">
+        <v>11</v>
+      </c>
+      <c r="D291" t="s">
         <v>13</v>
-      </c>
-      <c r="D291" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -4528,10 +4528,10 @@
         <v>1128</v>
       </c>
       <c r="C292">
+        <v>13</v>
+      </c>
+      <c r="D292" t="s">
         <v>14</v>
-      </c>
-      <c r="D292" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4539,13 +4539,13 @@
         <v>291</v>
       </c>
       <c r="B293">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="C293">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D293" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -4553,13 +4553,13 @@
         <v>292</v>
       </c>
       <c r="B294">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C294">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D294" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -4573,7 +4573,7 @@
         <v>4</v>
       </c>
       <c r="D295" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -4584,10 +4584,10 @@
         <v>1132</v>
       </c>
       <c r="C296">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D296" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -4595,13 +4595,13 @@
         <v>295</v>
       </c>
       <c r="B297">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C297">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D297" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4612,10 +4612,10 @@
         <v>1133</v>
       </c>
       <c r="C298">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D298" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -4626,10 +4626,10 @@
         <v>1133</v>
       </c>
       <c r="C299">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -4640,10 +4640,10 @@
         <v>1133</v>
       </c>
       <c r="C300">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D300" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4654,10 +4654,10 @@
         <v>1133</v>
       </c>
       <c r="C301">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D301" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4665,13 +4665,13 @@
         <v>300</v>
       </c>
       <c r="B302">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C302">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D302" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4679,13 +4679,13 @@
         <v>301</v>
       </c>
       <c r="B303">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C303">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D303" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4696,10 +4696,10 @@
         <v>1135</v>
       </c>
       <c r="C304">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D304" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -4710,10 +4710,10 @@
         <v>1135</v>
       </c>
       <c r="C305">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D305" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -4724,10 +4724,10 @@
         <v>1135</v>
       </c>
       <c r="C306">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D306" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -4738,10 +4738,10 @@
         <v>1135</v>
       </c>
       <c r="C307">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D307" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -4752,10 +4752,10 @@
         <v>1135</v>
       </c>
       <c r="C308">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D308" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -4763,13 +4763,13 @@
         <v>307</v>
       </c>
       <c r="B309">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C309">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D309" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -4780,10 +4780,10 @@
         <v>1136</v>
       </c>
       <c r="C310">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D310" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -4794,10 +4794,10 @@
         <v>1136</v>
       </c>
       <c r="C311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -4808,10 +4808,10 @@
         <v>1136</v>
       </c>
       <c r="C312">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D312" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -4822,7 +4822,7 @@
         <v>1136</v>
       </c>
       <c r="C313">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D313" t="s">
         <v>15</v>
@@ -4836,10 +4836,10 @@
         <v>1136</v>
       </c>
       <c r="C314">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D314" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -4850,10 +4850,10 @@
         <v>1136</v>
       </c>
       <c r="C315">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D315" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -4864,10 +4864,10 @@
         <v>1136</v>
       </c>
       <c r="C316">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D316" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -4878,10 +4878,10 @@
         <v>1136</v>
       </c>
       <c r="C317">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D317" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -4889,16 +4889,13 @@
         <v>316</v>
       </c>
       <c r="B318">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C318">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D318" t="s">
-        <v>16</v>
-      </c>
-      <c r="E318" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -4906,13 +4903,16 @@
         <v>317</v>
       </c>
       <c r="B319">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C319">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D319" t="s">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="E319" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -4923,10 +4923,10 @@
         <v>1138</v>
       </c>
       <c r="C320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D320" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -4937,10 +4937,10 @@
         <v>1138</v>
       </c>
       <c r="C321">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D321" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -4951,10 +4951,10 @@
         <v>1138</v>
       </c>
       <c r="C322">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D322" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -4965,10 +4965,10 @@
         <v>1138</v>
       </c>
       <c r="C323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D323" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4979,10 +4979,10 @@
         <v>1138</v>
       </c>
       <c r="C324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D324" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -4990,13 +4990,13 @@
         <v>323</v>
       </c>
       <c r="B325">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C325">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D325" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5007,10 +5007,10 @@
         <v>1139</v>
       </c>
       <c r="C326">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D326" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5021,10 +5021,10 @@
         <v>1139</v>
       </c>
       <c r="C327">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D327" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5035,10 +5035,10 @@
         <v>1139</v>
       </c>
       <c r="C328">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D328" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5049,10 +5049,10 @@
         <v>1139</v>
       </c>
       <c r="C329">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D329" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5063,10 +5063,10 @@
         <v>1139</v>
       </c>
       <c r="C330">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D330" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5077,10 +5077,10 @@
         <v>1139</v>
       </c>
       <c r="C331">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D331" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5091,10 +5091,10 @@
         <v>1139</v>
       </c>
       <c r="C332">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D332" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5105,10 +5105,10 @@
         <v>1139</v>
       </c>
       <c r="C333">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D333" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5116,13 +5116,13 @@
         <v>332</v>
       </c>
       <c r="B334">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C334">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D334" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5133,10 +5133,10 @@
         <v>1141</v>
       </c>
       <c r="C335">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D335" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5147,10 +5147,10 @@
         <v>1141</v>
       </c>
       <c r="C336">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5161,10 +5161,10 @@
         <v>1141</v>
       </c>
       <c r="C337">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D337" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5175,10 +5175,10 @@
         <v>1141</v>
       </c>
       <c r="C338">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D338" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5189,10 +5189,10 @@
         <v>1141</v>
       </c>
       <c r="C339">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D339" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5203,10 +5203,10 @@
         <v>1141</v>
       </c>
       <c r="C340">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D340" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5214,13 +5214,13 @@
         <v>339</v>
       </c>
       <c r="B341">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C341">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D341" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5231,10 +5231,10 @@
         <v>1143</v>
       </c>
       <c r="C342">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5245,10 +5245,10 @@
         <v>1143</v>
       </c>
       <c r="C343">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D343" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5259,10 +5259,10 @@
         <v>1143</v>
       </c>
       <c r="C344">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D344" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5273,10 +5273,10 @@
         <v>1143</v>
       </c>
       <c r="C345">
+        <v>13</v>
+      </c>
+      <c r="D345" t="s">
         <v>14</v>
-      </c>
-      <c r="D345" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5284,13 +5284,13 @@
         <v>344</v>
       </c>
       <c r="B346">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C346">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D346" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5301,10 +5301,10 @@
         <v>1144</v>
       </c>
       <c r="C347">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D347" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -5315,10 +5315,10 @@
         <v>1144</v>
       </c>
       <c r="C348">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D348" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -5329,10 +5329,10 @@
         <v>1144</v>
       </c>
       <c r="C349">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D349" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5340,13 +5340,13 @@
         <v>348</v>
       </c>
       <c r="B350">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C350">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D350" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5354,13 +5354,13 @@
         <v>349</v>
       </c>
       <c r="B351">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C351">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D351" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -5371,10 +5371,10 @@
         <v>1147</v>
       </c>
       <c r="C352">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D352" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -5385,10 +5385,10 @@
         <v>1147</v>
       </c>
       <c r="C353">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D353" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -5399,10 +5399,10 @@
         <v>1147</v>
       </c>
       <c r="C354">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D354" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -5410,13 +5410,13 @@
         <v>353</v>
       </c>
       <c r="B355">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C355">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D355" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -5427,10 +5427,10 @@
         <v>1148</v>
       </c>
       <c r="C356">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D356" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -5441,10 +5441,10 @@
         <v>1148</v>
       </c>
       <c r="C357">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D357" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -5455,10 +5455,10 @@
         <v>1148</v>
       </c>
       <c r="C358">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D358" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -5469,10 +5469,10 @@
         <v>1148</v>
       </c>
       <c r="C359">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D359" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -5483,13 +5483,10 @@
         <v>1148</v>
       </c>
       <c r="C360">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D360" t="s">
-        <v>12</v>
-      </c>
-      <c r="E360" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -5500,10 +5497,13 @@
         <v>1148</v>
       </c>
       <c r="C361">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D361" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="E361" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -5511,13 +5511,13 @@
         <v>360</v>
       </c>
       <c r="B362">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C362">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D362" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -5528,10 +5528,10 @@
         <v>1150</v>
       </c>
       <c r="C363">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D363" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -5542,10 +5542,10 @@
         <v>1150</v>
       </c>
       <c r="C364">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D364" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -5556,10 +5556,10 @@
         <v>1150</v>
       </c>
       <c r="C365">
+        <v>7</v>
+      </c>
+      <c r="D365" t="s">
         <v>8</v>
-      </c>
-      <c r="D365" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -5567,13 +5567,13 @@
         <v>364</v>
       </c>
       <c r="B366">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="C366">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D366" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -5584,10 +5584,10 @@
         <v>1155</v>
       </c>
       <c r="C367">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -5598,10 +5598,10 @@
         <v>1155</v>
       </c>
       <c r="C368">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D368" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -5612,10 +5612,10 @@
         <v>1155</v>
       </c>
       <c r="C369">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D369" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -5623,13 +5623,13 @@
         <v>368</v>
       </c>
       <c r="B370">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="C370">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D370" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -5637,16 +5637,13 @@
         <v>369</v>
       </c>
       <c r="B371">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C371">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D371" t="s">
-        <v>14</v>
-      </c>
-      <c r="E371" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -5660,6 +5657,9 @@
         <v>6</v>
       </c>
       <c r="D372" t="s">
+        <v>14</v>
+      </c>
+      <c r="E372" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5668,13 +5668,13 @@
         <v>371</v>
       </c>
       <c r="B373">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="C373">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D373" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -5685,10 +5685,10 @@
         <v>1162</v>
       </c>
       <c r="C374">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D374" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -5699,10 +5699,10 @@
         <v>1162</v>
       </c>
       <c r="C375">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D375" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -5710,13 +5710,13 @@
         <v>374</v>
       </c>
       <c r="B376">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="C376">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D376" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -5727,10 +5727,10 @@
         <v>1165</v>
       </c>
       <c r="C377">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D377" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -5741,10 +5741,10 @@
         <v>1165</v>
       </c>
       <c r="C378">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D378" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -5755,10 +5755,10 @@
         <v>1165</v>
       </c>
       <c r="C379">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D379" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -5769,10 +5769,10 @@
         <v>1165</v>
       </c>
       <c r="C380">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D380" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -5783,10 +5783,10 @@
         <v>1165</v>
       </c>
       <c r="C381">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D381" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -5797,10 +5797,10 @@
         <v>1165</v>
       </c>
       <c r="C382">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D382" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -5811,10 +5811,10 @@
         <v>1165</v>
       </c>
       <c r="C383">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D383" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -5822,13 +5822,13 @@
         <v>382</v>
       </c>
       <c r="B384">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C384">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D384" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -5839,10 +5839,10 @@
         <v>1166</v>
       </c>
       <c r="C385">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D385" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -5853,10 +5853,10 @@
         <v>1166</v>
       </c>
       <c r="C386">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D386" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5867,10 +5867,10 @@
         <v>1166</v>
       </c>
       <c r="C387">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D387" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -5881,10 +5881,10 @@
         <v>1166</v>
       </c>
       <c r="C388">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D388" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5895,10 +5895,10 @@
         <v>1166</v>
       </c>
       <c r="C389">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D389" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5909,10 +5909,10 @@
         <v>1166</v>
       </c>
       <c r="C390">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D390" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -5923,10 +5923,10 @@
         <v>1166</v>
       </c>
       <c r="C391">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D391" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5937,10 +5937,10 @@
         <v>1166</v>
       </c>
       <c r="C392">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D392" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -5948,13 +5948,13 @@
         <v>391</v>
       </c>
       <c r="B393">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C393">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D393" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -5965,10 +5965,10 @@
         <v>1167</v>
       </c>
       <c r="C394">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D394" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -5979,10 +5979,10 @@
         <v>1167</v>
       </c>
       <c r="C395">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D395" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -5990,13 +5990,13 @@
         <v>394</v>
       </c>
       <c r="B396">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C396">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D396" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6007,10 +6007,10 @@
         <v>1168</v>
       </c>
       <c r="C397">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D397" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6021,10 +6021,10 @@
         <v>1168</v>
       </c>
       <c r="C398">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D398" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6035,10 +6035,10 @@
         <v>1168</v>
       </c>
       <c r="C399">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D399" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6049,10 +6049,10 @@
         <v>1168</v>
       </c>
       <c r="C400">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D400" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6063,10 +6063,10 @@
         <v>1168</v>
       </c>
       <c r="C401">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D401" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6077,10 +6077,10 @@
         <v>1168</v>
       </c>
       <c r="C402">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D402" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6088,13 +6088,13 @@
         <v>401</v>
       </c>
       <c r="B403">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C403">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D403" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6105,10 +6105,10 @@
         <v>1169</v>
       </c>
       <c r="C404">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D404" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6119,10 +6119,10 @@
         <v>1169</v>
       </c>
       <c r="C405">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D405" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6133,10 +6133,10 @@
         <v>1169</v>
       </c>
       <c r="C406">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D406" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6147,10 +6147,10 @@
         <v>1169</v>
       </c>
       <c r="C407">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D407" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6161,10 +6161,10 @@
         <v>1169</v>
       </c>
       <c r="C408">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D408" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6175,10 +6175,10 @@
         <v>1169</v>
       </c>
       <c r="C409">
+        <v>13</v>
+      </c>
+      <c r="D409" t="s">
         <v>14</v>
-      </c>
-      <c r="D409" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6186,13 +6186,13 @@
         <v>408</v>
       </c>
       <c r="B410">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C410">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D410" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6203,10 +6203,10 @@
         <v>1170</v>
       </c>
       <c r="C411">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D411" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6217,10 +6217,10 @@
         <v>1170</v>
       </c>
       <c r="C412">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D412" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6231,10 +6231,10 @@
         <v>1170</v>
       </c>
       <c r="C413">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D413" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -6245,10 +6245,10 @@
         <v>1170</v>
       </c>
       <c r="C414">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D414" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -6259,10 +6259,10 @@
         <v>1170</v>
       </c>
       <c r="C415">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D415" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -6273,10 +6273,10 @@
         <v>1170</v>
       </c>
       <c r="C416">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D416" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -6287,10 +6287,10 @@
         <v>1170</v>
       </c>
       <c r="C417">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D417" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -6298,13 +6298,13 @@
         <v>416</v>
       </c>
       <c r="B418">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C418">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D418" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -6315,10 +6315,10 @@
         <v>1171</v>
       </c>
       <c r="C419">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D419" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -6329,10 +6329,10 @@
         <v>1171</v>
       </c>
       <c r="C420">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D420" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -6343,10 +6343,10 @@
         <v>1171</v>
       </c>
       <c r="C421">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D421" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -6357,10 +6357,10 @@
         <v>1171</v>
       </c>
       <c r="C422">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D422" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -6368,13 +6368,13 @@
         <v>421</v>
       </c>
       <c r="B423">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C423">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D423" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -6385,10 +6385,10 @@
         <v>1172</v>
       </c>
       <c r="C424">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D424" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -6399,10 +6399,10 @@
         <v>1172</v>
       </c>
       <c r="C425">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D425" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -6413,10 +6413,10 @@
         <v>1172</v>
       </c>
       <c r="C426">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D426" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -6424,13 +6424,13 @@
         <v>425</v>
       </c>
       <c r="B427">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C427">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D427" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -6441,10 +6441,10 @@
         <v>1173</v>
       </c>
       <c r="C428">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D428" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -6455,10 +6455,10 @@
         <v>1173</v>
       </c>
       <c r="C429">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D429" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -6469,10 +6469,10 @@
         <v>1173</v>
       </c>
       <c r="C430">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D430" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -6483,10 +6483,10 @@
         <v>1173</v>
       </c>
       <c r="C431">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D431" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -6497,10 +6497,10 @@
         <v>1173</v>
       </c>
       <c r="C432">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D432" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -6511,10 +6511,10 @@
         <v>1173</v>
       </c>
       <c r="C433">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D433" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -6525,10 +6525,10 @@
         <v>1173</v>
       </c>
       <c r="C434">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D434" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -6539,10 +6539,10 @@
         <v>1173</v>
       </c>
       <c r="C435">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D435" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6553,10 +6553,10 @@
         <v>1173</v>
       </c>
       <c r="C436">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D436" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -6567,10 +6567,10 @@
         <v>1173</v>
       </c>
       <c r="C437">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D437" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -6578,13 +6578,13 @@
         <v>436</v>
       </c>
       <c r="B438">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C438">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D438" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -6595,10 +6595,10 @@
         <v>1174</v>
       </c>
       <c r="C439">
+        <v>4</v>
+      </c>
+      <c r="D439" t="s">
         <v>7</v>
-      </c>
-      <c r="D439" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -6606,13 +6606,13 @@
         <v>438</v>
       </c>
       <c r="B440">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C440">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D440" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -6623,10 +6623,10 @@
         <v>1175</v>
       </c>
       <c r="C441">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D441" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -6634,13 +6634,13 @@
         <v>440</v>
       </c>
       <c r="B442">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C442">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D442" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -6651,10 +6651,10 @@
         <v>1176</v>
       </c>
       <c r="C443">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D443" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -6665,10 +6665,10 @@
         <v>1176</v>
       </c>
       <c r="C444">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D444" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -6676,13 +6676,13 @@
         <v>443</v>
       </c>
       <c r="B445">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C445">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D445" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -6693,10 +6693,10 @@
         <v>1177</v>
       </c>
       <c r="C446">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D446" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6707,10 +6707,10 @@
         <v>1177</v>
       </c>
       <c r="C447">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D447" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -6721,10 +6721,10 @@
         <v>1177</v>
       </c>
       <c r="C448">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D448" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -6735,10 +6735,10 @@
         <v>1177</v>
       </c>
       <c r="C449">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D449" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -6752,7 +6752,7 @@
         <v>10</v>
       </c>
       <c r="D450" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -6760,13 +6760,13 @@
         <v>449</v>
       </c>
       <c r="B451">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C451">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D451" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -6777,10 +6777,10 @@
         <v>1178</v>
       </c>
       <c r="C452">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D452" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -6791,10 +6791,10 @@
         <v>1178</v>
       </c>
       <c r="C453">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D453" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -6805,10 +6805,10 @@
         <v>1178</v>
       </c>
       <c r="C454">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D454" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -6819,10 +6819,10 @@
         <v>1178</v>
       </c>
       <c r="C455">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D455" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -6833,10 +6833,10 @@
         <v>1178</v>
       </c>
       <c r="C456">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D456" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -6844,13 +6844,13 @@
         <v>455</v>
       </c>
       <c r="B457">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C457">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D457" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -6861,10 +6861,10 @@
         <v>1180</v>
       </c>
       <c r="C458">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D458" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -6875,10 +6875,10 @@
         <v>1180</v>
       </c>
       <c r="C459">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D459" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -6889,10 +6889,10 @@
         <v>1180</v>
       </c>
       <c r="C460">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D460" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -6903,10 +6903,10 @@
         <v>1180</v>
       </c>
       <c r="C461">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D461" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -6917,10 +6917,10 @@
         <v>1180</v>
       </c>
       <c r="C462">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D462" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -6931,10 +6931,10 @@
         <v>1180</v>
       </c>
       <c r="C463">
+        <v>11</v>
+      </c>
+      <c r="D463" t="s">
         <v>12</v>
-      </c>
-      <c r="D463" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -6942,13 +6942,13 @@
         <v>462</v>
       </c>
       <c r="B464">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C464">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D464" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -6959,10 +6959,10 @@
         <v>1181</v>
       </c>
       <c r="C465">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D465" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -6973,10 +6973,10 @@
         <v>1181</v>
       </c>
       <c r="C466">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D466" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -6987,10 +6987,10 @@
         <v>1181</v>
       </c>
       <c r="C467">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D467" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -6998,13 +6998,13 @@
         <v>466</v>
       </c>
       <c r="B468">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C468">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D468" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -7015,10 +7015,10 @@
         <v>1182</v>
       </c>
       <c r="C469">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D469" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -7029,10 +7029,10 @@
         <v>1182</v>
       </c>
       <c r="C470">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D470" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -7043,10 +7043,10 @@
         <v>1182</v>
       </c>
       <c r="C471">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D471" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -7057,10 +7057,10 @@
         <v>1182</v>
       </c>
       <c r="C472">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D472" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -7071,10 +7071,10 @@
         <v>1182</v>
       </c>
       <c r="C473">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D473" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -7085,7 +7085,7 @@
         <v>1182</v>
       </c>
       <c r="C474">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D474" t="s">
         <v>14</v>
@@ -7099,10 +7099,10 @@
         <v>1182</v>
       </c>
       <c r="C475">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D475" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -7110,13 +7110,13 @@
         <v>474</v>
       </c>
       <c r="B476">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C476">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D476" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -7127,10 +7127,10 @@
         <v>1184</v>
       </c>
       <c r="C477">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D477" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -7141,10 +7141,10 @@
         <v>1184</v>
       </c>
       <c r="C478">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D478" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -7155,10 +7155,10 @@
         <v>1184</v>
       </c>
       <c r="C479">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D479" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -7169,10 +7169,10 @@
         <v>1184</v>
       </c>
       <c r="C480">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D480" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -7180,13 +7180,13 @@
         <v>479</v>
       </c>
       <c r="B481">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C481">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D481" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -7197,10 +7197,10 @@
         <v>1185</v>
       </c>
       <c r="C482">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D482" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -7211,10 +7211,10 @@
         <v>1185</v>
       </c>
       <c r="C483">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D483" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -7225,10 +7225,10 @@
         <v>1185</v>
       </c>
       <c r="C484">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D484" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -7236,13 +7236,13 @@
         <v>483</v>
       </c>
       <c r="B485">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C485">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D485" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -7253,10 +7253,10 @@
         <v>1187</v>
       </c>
       <c r="C486">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D486" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -7267,10 +7267,10 @@
         <v>1187</v>
       </c>
       <c r="C487">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D487" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -7281,10 +7281,10 @@
         <v>1187</v>
       </c>
       <c r="C488">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D488" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -7295,10 +7295,10 @@
         <v>1187</v>
       </c>
       <c r="C489">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D489" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -7309,10 +7309,10 @@
         <v>1187</v>
       </c>
       <c r="C490">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D490" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -7323,10 +7323,10 @@
         <v>1187</v>
       </c>
       <c r="C491">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D491" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -7334,13 +7334,13 @@
         <v>490</v>
       </c>
       <c r="B492">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C492">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D492" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -7351,10 +7351,10 @@
         <v>1188</v>
       </c>
       <c r="C493">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D493" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -7362,13 +7362,13 @@
         <v>492</v>
       </c>
       <c r="B494">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C494">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D494" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -7379,10 +7379,10 @@
         <v>1189</v>
       </c>
       <c r="C495">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D495" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -7393,10 +7393,10 @@
         <v>1189</v>
       </c>
       <c r="C496">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D496" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -7407,10 +7407,10 @@
         <v>1189</v>
       </c>
       <c r="C497">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D497" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -7421,10 +7421,10 @@
         <v>1189</v>
       </c>
       <c r="C498">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D498" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -7435,10 +7435,10 @@
         <v>1189</v>
       </c>
       <c r="C499">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D499" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -7449,10 +7449,10 @@
         <v>1189</v>
       </c>
       <c r="C500">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D500" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -7463,10 +7463,10 @@
         <v>1189</v>
       </c>
       <c r="C501">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D501" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -7477,10 +7477,10 @@
         <v>1189</v>
       </c>
       <c r="C502">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D502" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -7491,10 +7491,10 @@
         <v>1189</v>
       </c>
       <c r="C503">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D503" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -7502,13 +7502,13 @@
         <v>502</v>
       </c>
       <c r="B504">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C504">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D504" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -7519,10 +7519,10 @@
         <v>1190</v>
       </c>
       <c r="C505">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D505" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -7533,10 +7533,10 @@
         <v>1190</v>
       </c>
       <c r="C506">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D506" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -7547,10 +7547,10 @@
         <v>1190</v>
       </c>
       <c r="C507">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D507" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -7561,10 +7561,10 @@
         <v>1190</v>
       </c>
       <c r="C508">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D508" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -7572,13 +7572,13 @@
         <v>507</v>
       </c>
       <c r="B509">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C509">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D509" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -7589,10 +7589,10 @@
         <v>1191</v>
       </c>
       <c r="C510">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D510" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -7603,10 +7603,10 @@
         <v>1191</v>
       </c>
       <c r="C511">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D511" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -7617,10 +7617,10 @@
         <v>1191</v>
       </c>
       <c r="C512">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D512" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -7631,7 +7631,7 @@
         <v>1191</v>
       </c>
       <c r="C513">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D513" t="s">
         <v>9</v>
@@ -7645,10 +7645,10 @@
         <v>1191</v>
       </c>
       <c r="C514">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D514" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -7659,10 +7659,10 @@
         <v>1191</v>
       </c>
       <c r="C515">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D515" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -7673,10 +7673,10 @@
         <v>1191</v>
       </c>
       <c r="C516">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D516" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -7684,13 +7684,13 @@
         <v>515</v>
       </c>
       <c r="B517">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C517">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D517" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -7701,10 +7701,10 @@
         <v>1192</v>
       </c>
       <c r="C518">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D518" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -7715,10 +7715,10 @@
         <v>1192</v>
       </c>
       <c r="C519">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D519" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -7729,10 +7729,10 @@
         <v>1192</v>
       </c>
       <c r="C520">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D520" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -7740,13 +7740,13 @@
         <v>519</v>
       </c>
       <c r="B521">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C521">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D521" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -7757,10 +7757,10 @@
         <v>1194</v>
       </c>
       <c r="C522">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D522" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -7771,10 +7771,10 @@
         <v>1194</v>
       </c>
       <c r="C523">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D523" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -7785,10 +7785,10 @@
         <v>1194</v>
       </c>
       <c r="C524">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D524" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -7799,10 +7799,10 @@
         <v>1194</v>
       </c>
       <c r="C525">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D525" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -7810,13 +7810,13 @@
         <v>524</v>
       </c>
       <c r="B526">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C526">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D526" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -7824,7 +7824,7 @@
         <v>525</v>
       </c>
       <c r="B527">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C527">
         <v>0</v>
@@ -7841,10 +7841,10 @@
         <v>1197</v>
       </c>
       <c r="C528">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D528" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -7855,10 +7855,10 @@
         <v>1197</v>
       </c>
       <c r="C529">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D529" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -7869,10 +7869,10 @@
         <v>1197</v>
       </c>
       <c r="C530">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D530" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -7880,13 +7880,13 @@
         <v>529</v>
       </c>
       <c r="B531">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C531">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D531" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -7897,10 +7897,10 @@
         <v>1198</v>
       </c>
       <c r="C532">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D532" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -7911,10 +7911,10 @@
         <v>1198</v>
       </c>
       <c r="C533">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D533" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -7925,10 +7925,10 @@
         <v>1198</v>
       </c>
       <c r="C534">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D534" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -7939,10 +7939,10 @@
         <v>1198</v>
       </c>
       <c r="C535">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D535" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -7953,10 +7953,10 @@
         <v>1198</v>
       </c>
       <c r="C536">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D536" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -7967,10 +7967,10 @@
         <v>1198</v>
       </c>
       <c r="C537">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D537" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -7978,13 +7978,13 @@
         <v>536</v>
       </c>
       <c r="B538">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C538">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D538" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -7995,10 +7995,10 @@
         <v>1200</v>
       </c>
       <c r="C539">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D539" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -8009,10 +8009,10 @@
         <v>1200</v>
       </c>
       <c r="C540">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D540" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -8023,10 +8023,10 @@
         <v>1200</v>
       </c>
       <c r="C541">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D541" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -8037,10 +8037,10 @@
         <v>1200</v>
       </c>
       <c r="C542">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D542" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -8051,7 +8051,7 @@
         <v>1200</v>
       </c>
       <c r="C543">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D543" t="s">
         <v>9</v>
@@ -8065,10 +8065,10 @@
         <v>1200</v>
       </c>
       <c r="C544">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D544" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -8079,10 +8079,10 @@
         <v>1200</v>
       </c>
       <c r="C545">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D545" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -8093,10 +8093,10 @@
         <v>1200</v>
       </c>
       <c r="C546">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D546" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -8107,10 +8107,10 @@
         <v>1200</v>
       </c>
       <c r="C547">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D547" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -8118,13 +8118,13 @@
         <v>546</v>
       </c>
       <c r="B548">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C548">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D548" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -8135,10 +8135,10 @@
         <v>1201</v>
       </c>
       <c r="C549">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D549" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -8149,10 +8149,10 @@
         <v>1201</v>
       </c>
       <c r="C550">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D550" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -8160,13 +8160,13 @@
         <v>549</v>
       </c>
       <c r="B551">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C551">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D551" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -8177,10 +8177,10 @@
         <v>1202</v>
       </c>
       <c r="C552">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D552" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -8191,10 +8191,10 @@
         <v>1202</v>
       </c>
       <c r="C553">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D553" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -8205,10 +8205,10 @@
         <v>1202</v>
       </c>
       <c r="C554">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D554" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -8216,13 +8216,13 @@
         <v>553</v>
       </c>
       <c r="B555">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C555">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D555" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -8233,10 +8233,10 @@
         <v>1203</v>
       </c>
       <c r="C556">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D556" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -8247,10 +8247,10 @@
         <v>1203</v>
       </c>
       <c r="C557">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D557" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -8258,13 +8258,13 @@
         <v>556</v>
       </c>
       <c r="B558">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C558">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D558" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -8275,10 +8275,10 @@
         <v>1204</v>
       </c>
       <c r="C559">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D559" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -8289,10 +8289,10 @@
         <v>1204</v>
       </c>
       <c r="C560">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D560" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -8303,10 +8303,10 @@
         <v>1204</v>
       </c>
       <c r="C561">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D561" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -8317,10 +8317,10 @@
         <v>1204</v>
       </c>
       <c r="C562">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D562" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -8331,10 +8331,10 @@
         <v>1204</v>
       </c>
       <c r="C563">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D563" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -8345,10 +8345,10 @@
         <v>1204</v>
       </c>
       <c r="C564">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D564" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -8359,10 +8359,10 @@
         <v>1204</v>
       </c>
       <c r="C565">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D565" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -8373,10 +8373,10 @@
         <v>1204</v>
       </c>
       <c r="C566">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D566" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -8384,13 +8384,13 @@
         <v>565</v>
       </c>
       <c r="B567">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C567">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D567" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -8398,13 +8398,13 @@
         <v>566</v>
       </c>
       <c r="B568">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C568">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D568" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -8415,10 +8415,10 @@
         <v>1207</v>
       </c>
       <c r="C569">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D569" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -8429,10 +8429,10 @@
         <v>1207</v>
       </c>
       <c r="C570">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D570" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -8443,10 +8443,10 @@
         <v>1207</v>
       </c>
       <c r="C571">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D571" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -8457,10 +8457,10 @@
         <v>1207</v>
       </c>
       <c r="C572">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D572" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -8471,10 +8471,10 @@
         <v>1207</v>
       </c>
       <c r="C573">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D573" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -8485,10 +8485,10 @@
         <v>1207</v>
       </c>
       <c r="C574">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D574" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -8496,13 +8496,13 @@
         <v>573</v>
       </c>
       <c r="B575">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C575">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D575" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -8513,10 +8513,10 @@
         <v>1208</v>
       </c>
       <c r="C576">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D576" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -8527,10 +8527,10 @@
         <v>1208</v>
       </c>
       <c r="C577">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D577" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -8538,13 +8538,13 @@
         <v>576</v>
       </c>
       <c r="B578">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C578">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D578" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -8555,10 +8555,10 @@
         <v>1212</v>
       </c>
       <c r="C579">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D579" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -8569,10 +8569,10 @@
         <v>1212</v>
       </c>
       <c r="C580">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D580" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -8583,10 +8583,10 @@
         <v>1212</v>
       </c>
       <c r="C581">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D581" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -8597,10 +8597,10 @@
         <v>1212</v>
       </c>
       <c r="C582">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D582" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -8608,13 +8608,13 @@
         <v>581</v>
       </c>
       <c r="B583">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C583">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D583" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -8625,10 +8625,10 @@
         <v>1213</v>
       </c>
       <c r="C584">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D584" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -8639,10 +8639,10 @@
         <v>1213</v>
       </c>
       <c r="C585">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D585" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -8653,10 +8653,10 @@
         <v>1213</v>
       </c>
       <c r="C586">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D586" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -8667,10 +8667,10 @@
         <v>1213</v>
       </c>
       <c r="C587">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D587" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -8681,10 +8681,10 @@
         <v>1213</v>
       </c>
       <c r="C588">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D588" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -8695,7 +8695,7 @@
         <v>1213</v>
       </c>
       <c r="C589">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D589" t="s">
         <v>8</v>
@@ -8706,13 +8706,13 @@
         <v>588</v>
       </c>
       <c r="B590">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C590">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D590" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -8723,10 +8723,10 @@
         <v>1214</v>
       </c>
       <c r="C591">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D591" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -8737,10 +8737,10 @@
         <v>1214</v>
       </c>
       <c r="C592">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D592" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -8751,10 +8751,10 @@
         <v>1214</v>
       </c>
       <c r="C593">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D593" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -8765,10 +8765,10 @@
         <v>1214</v>
       </c>
       <c r="C594">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D594" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -8776,13 +8776,13 @@
         <v>593</v>
       </c>
       <c r="B595">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C595">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D595" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -8793,10 +8793,10 @@
         <v>1215</v>
       </c>
       <c r="C596">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D596" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -8807,10 +8807,10 @@
         <v>1215</v>
       </c>
       <c r="C597">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D597" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -8821,10 +8821,10 @@
         <v>1215</v>
       </c>
       <c r="C598">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D598" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -8832,13 +8832,13 @@
         <v>597</v>
       </c>
       <c r="B599">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="C599">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D599" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -8849,10 +8849,10 @@
         <v>1216</v>
       </c>
       <c r="C600">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D600" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -8863,10 +8863,10 @@
         <v>1216</v>
       </c>
       <c r="C601">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D601" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -8874,13 +8874,13 @@
         <v>600</v>
       </c>
       <c r="B602">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="C602">
         <v>2</v>
       </c>
       <c r="D602" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -8891,10 +8891,10 @@
         <v>1217</v>
       </c>
       <c r="C603">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D603" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -8905,10 +8905,10 @@
         <v>1217</v>
       </c>
       <c r="C604">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D604" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -8919,10 +8919,10 @@
         <v>1217</v>
       </c>
       <c r="C605">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D605" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -8933,10 +8933,10 @@
         <v>1217</v>
       </c>
       <c r="C606">
+        <v>6</v>
+      </c>
+      <c r="D606" t="s">
         <v>8</v>
-      </c>
-      <c r="D606" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -8944,13 +8944,13 @@
         <v>605</v>
       </c>
       <c r="B607">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C607">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D607" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -8961,10 +8961,10 @@
         <v>1218</v>
       </c>
       <c r="C608">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D608" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -8975,10 +8975,10 @@
         <v>1218</v>
       </c>
       <c r="C609">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D609" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -8989,10 +8989,10 @@
         <v>1218</v>
       </c>
       <c r="C610">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D610" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -9000,13 +9000,13 @@
         <v>609</v>
       </c>
       <c r="B611">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C611">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D611" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -9017,10 +9017,10 @@
         <v>1219</v>
       </c>
       <c r="C612">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D612" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -9031,10 +9031,10 @@
         <v>1219</v>
       </c>
       <c r="C613">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D613" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -9045,7 +9045,7 @@
         <v>1219</v>
       </c>
       <c r="C614">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D614" t="s">
         <v>6</v>
@@ -9059,10 +9059,10 @@
         <v>1219</v>
       </c>
       <c r="C615">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D615" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="616" spans="1:4">
@@ -9073,7 +9073,7 @@
         <v>1219</v>
       </c>
       <c r="C616">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D616" t="s">
         <v>16</v>
@@ -9087,10 +9087,10 @@
         <v>1219</v>
       </c>
       <c r="C617">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D617" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -9101,10 +9101,10 @@
         <v>1219</v>
       </c>
       <c r="C618">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D618" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="619" spans="1:4">
@@ -9115,7 +9115,7 @@
         <v>1219</v>
       </c>
       <c r="C619">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D619" t="s">
         <v>11</v>
@@ -9129,10 +9129,10 @@
         <v>1219</v>
       </c>
       <c r="C620">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D620" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="621" spans="1:4">
@@ -9143,10 +9143,10 @@
         <v>1219</v>
       </c>
       <c r="C621">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D621" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -9157,10 +9157,10 @@
         <v>1219</v>
       </c>
       <c r="C622">
+        <v>12</v>
+      </c>
+      <c r="D622" t="s">
         <v>13</v>
-      </c>
-      <c r="D622" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -9168,13 +9168,13 @@
         <v>621</v>
       </c>
       <c r="B623">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C623">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D623" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -9185,10 +9185,10 @@
         <v>1220</v>
       </c>
       <c r="C624">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D624" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="625" spans="1:5">
@@ -9199,10 +9199,10 @@
         <v>1220</v>
       </c>
       <c r="C625">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D625" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="626" spans="1:5">
@@ -9210,13 +9210,13 @@
         <v>624</v>
       </c>
       <c r="B626">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C626">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D626" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="627" spans="1:5">
@@ -9227,10 +9227,10 @@
         <v>1221</v>
       </c>
       <c r="C627">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D627" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="628" spans="1:5">
@@ -9241,10 +9241,10 @@
         <v>1221</v>
       </c>
       <c r="C628">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D628" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="629" spans="1:5">
@@ -9255,10 +9255,10 @@
         <v>1221</v>
       </c>
       <c r="C629">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D629" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="630" spans="1:5">
@@ -9269,10 +9269,10 @@
         <v>1221</v>
       </c>
       <c r="C630">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D630" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="631" spans="1:5">
@@ -9283,10 +9283,10 @@
         <v>1221</v>
       </c>
       <c r="C631">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D631" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="632" spans="1:5">
@@ -9297,10 +9297,10 @@
         <v>1221</v>
       </c>
       <c r="C632">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D632" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="633" spans="1:5">
@@ -9311,10 +9311,10 @@
         <v>1221</v>
       </c>
       <c r="C633">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D633" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="634" spans="1:5">
@@ -9325,10 +9325,10 @@
         <v>1221</v>
       </c>
       <c r="C634">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D634" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="635" spans="1:5">
@@ -9336,13 +9336,13 @@
         <v>633</v>
       </c>
       <c r="B635">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C635">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D635" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="636" spans="1:5">
@@ -9353,10 +9353,10 @@
         <v>1223</v>
       </c>
       <c r="C636">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D636" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="637" spans="1:5">
@@ -9367,10 +9367,10 @@
         <v>1223</v>
       </c>
       <c r="C637">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D637" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="638" spans="1:5">
@@ -9381,10 +9381,10 @@
         <v>1223</v>
       </c>
       <c r="C638">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D638" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="639" spans="1:5">
@@ -9395,13 +9395,10 @@
         <v>1223</v>
       </c>
       <c r="C639">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D639" t="s">
-        <v>17</v>
-      </c>
-      <c r="E639" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="640" spans="1:5">
@@ -9412,10 +9409,13 @@
         <v>1223</v>
       </c>
       <c r="C640">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D640" t="s">
-        <v>9</v>
+        <v>17</v>
+      </c>
+      <c r="E640" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="641" spans="1:4">
@@ -9426,10 +9426,10 @@
         <v>1223</v>
       </c>
       <c r="C641">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D641" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="642" spans="1:4">
@@ -9437,13 +9437,13 @@
         <v>640</v>
       </c>
       <c r="B642">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="C642">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D642" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="643" spans="1:4">
@@ -9454,10 +9454,10 @@
         <v>1224</v>
       </c>
       <c r="C643">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D643" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="644" spans="1:4">
@@ -9468,10 +9468,10 @@
         <v>1224</v>
       </c>
       <c r="C644">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D644" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="645" spans="1:4">
@@ -9482,10 +9482,10 @@
         <v>1224</v>
       </c>
       <c r="C645">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D645" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="646" spans="1:4">
@@ -9496,10 +9496,10 @@
         <v>1224</v>
       </c>
       <c r="C646">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D646" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="647" spans="1:4">
@@ -9507,13 +9507,13 @@
         <v>645</v>
       </c>
       <c r="B647">
-        <v>1231</v>
+        <v>1224</v>
       </c>
       <c r="C647">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D647" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="648" spans="1:4">
@@ -9524,10 +9524,10 @@
         <v>1231</v>
       </c>
       <c r="C648">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D648" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="649" spans="1:4">
@@ -9538,10 +9538,10 @@
         <v>1231</v>
       </c>
       <c r="C649">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D649" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="650" spans="1:4">
@@ -9552,10 +9552,10 @@
         <v>1231</v>
       </c>
       <c r="C650">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D650" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="651" spans="1:4">
@@ -9566,10 +9566,10 @@
         <v>1231</v>
       </c>
       <c r="C651">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D651" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="652" spans="1:4">
@@ -9577,13 +9577,13 @@
         <v>650</v>
       </c>
       <c r="B652">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C652">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D652" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="653" spans="1:4">
@@ -9594,10 +9594,10 @@
         <v>1232</v>
       </c>
       <c r="C653">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D653" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="654" spans="1:4">
@@ -9608,10 +9608,10 @@
         <v>1232</v>
       </c>
       <c r="C654">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D654" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="655" spans="1:4">
@@ -9622,10 +9622,10 @@
         <v>1232</v>
       </c>
       <c r="C655">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D655" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="656" spans="1:4">
@@ -9636,10 +9636,10 @@
         <v>1232</v>
       </c>
       <c r="C656">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D656" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="657" spans="1:5">
@@ -9650,10 +9650,10 @@
         <v>1232</v>
       </c>
       <c r="C657">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D657" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="658" spans="1:5">
@@ -9664,7 +9664,7 @@
         <v>1232</v>
       </c>
       <c r="C658">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D658" t="s">
         <v>9</v>
@@ -9678,7 +9678,7 @@
         <v>1232</v>
       </c>
       <c r="C659">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D659" t="s">
         <v>9</v>
@@ -9692,10 +9692,10 @@
         <v>1232</v>
       </c>
       <c r="C660">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D660" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="661" spans="1:5">
@@ -9706,7 +9706,7 @@
         <v>1232</v>
       </c>
       <c r="C661">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D661" t="s">
         <v>13</v>
@@ -9717,13 +9717,13 @@
         <v>660</v>
       </c>
       <c r="B662">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C662">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D662" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="663" spans="1:5">
@@ -9734,10 +9734,10 @@
         <v>1233</v>
       </c>
       <c r="C663">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D663" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="664" spans="1:5">
@@ -9745,13 +9745,13 @@
         <v>662</v>
       </c>
       <c r="B664">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C664">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D664" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="665" spans="1:5">
@@ -9762,10 +9762,10 @@
         <v>1234</v>
       </c>
       <c r="C665">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D665" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="666" spans="1:5">
@@ -9773,16 +9773,13 @@
         <v>664</v>
       </c>
       <c r="B666">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C666">
         <v>1</v>
       </c>
       <c r="D666" t="s">
-        <v>10</v>
-      </c>
-      <c r="E666" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="667" spans="1:5">
@@ -9790,13 +9787,16 @@
         <v>665</v>
       </c>
       <c r="B667">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C667">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D667" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="E667" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="668" spans="1:5">
@@ -9807,10 +9807,10 @@
         <v>1236</v>
       </c>
       <c r="C668">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D668" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="669" spans="1:5">
@@ -9821,10 +9821,10 @@
         <v>1236</v>
       </c>
       <c r="C669">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D669" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="670" spans="1:5">
@@ -9835,10 +9835,10 @@
         <v>1236</v>
       </c>
       <c r="C670">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D670" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="671" spans="1:5">
@@ -9849,13 +9849,10 @@
         <v>1236</v>
       </c>
       <c r="C671">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D671" t="s">
-        <v>14</v>
-      </c>
-      <c r="E671" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="672" spans="1:5">
@@ -9863,13 +9860,16 @@
         <v>670</v>
       </c>
       <c r="B672">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C672">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D672" t="s">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="E672" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="673" spans="1:4">
@@ -9880,10 +9880,10 @@
         <v>1238</v>
       </c>
       <c r="C673">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D673" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="674" spans="1:4">
@@ -9894,10 +9894,10 @@
         <v>1238</v>
       </c>
       <c r="C674">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D674" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="675" spans="1:4">
@@ -9905,13 +9905,13 @@
         <v>673</v>
       </c>
       <c r="B675">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C675">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D675" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="676" spans="1:4">
@@ -9922,10 +9922,10 @@
         <v>1239</v>
       </c>
       <c r="C676">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D676" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -9936,10 +9936,10 @@
         <v>1239</v>
       </c>
       <c r="C677">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D677" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -9950,10 +9950,10 @@
         <v>1239</v>
       </c>
       <c r="C678">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D678" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -9964,10 +9964,10 @@
         <v>1239</v>
       </c>
       <c r="C679">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D679" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -9978,10 +9978,10 @@
         <v>1239</v>
       </c>
       <c r="C680">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D680" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -9989,13 +9989,13 @@
         <v>679</v>
       </c>
       <c r="B681">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C681">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D681" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -10006,10 +10006,10 @@
         <v>1240</v>
       </c>
       <c r="C682">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D682" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -10020,10 +10020,10 @@
         <v>1240</v>
       </c>
       <c r="C683">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D683" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="684" spans="1:4">
@@ -10031,13 +10031,13 @@
         <v>682</v>
       </c>
       <c r="B684">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C684">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D684" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="685" spans="1:4">
@@ -10048,10 +10048,10 @@
         <v>1241</v>
       </c>
       <c r="C685">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D685" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="686" spans="1:4">
@@ -10059,13 +10059,13 @@
         <v>684</v>
       </c>
       <c r="B686">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C686">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D686" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="687" spans="1:4">
@@ -10076,10 +10076,10 @@
         <v>1242</v>
       </c>
       <c r="C687">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D687" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="688" spans="1:4">
@@ -10087,13 +10087,13 @@
         <v>686</v>
       </c>
       <c r="B688">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C688">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D688" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="689" spans="1:4">
@@ -10104,10 +10104,10 @@
         <v>1243</v>
       </c>
       <c r="C689">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D689" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="690" spans="1:4">
@@ -10118,10 +10118,10 @@
         <v>1243</v>
       </c>
       <c r="C690">
+        <v>2</v>
+      </c>
+      <c r="D690" t="s">
         <v>7</v>
-      </c>
-      <c r="D690" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="691" spans="1:4">
@@ -10129,13 +10129,13 @@
         <v>689</v>
       </c>
       <c r="B691">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C691">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D691" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="692" spans="1:4">
@@ -10146,10 +10146,10 @@
         <v>1245</v>
       </c>
       <c r="C692">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D692" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="693" spans="1:4">
@@ -10160,10 +10160,10 @@
         <v>1245</v>
       </c>
       <c r="C693">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D693" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="694" spans="1:4">
@@ -10174,10 +10174,10 @@
         <v>1245</v>
       </c>
       <c r="C694">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D694" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="695" spans="1:4">
@@ -10188,10 +10188,10 @@
         <v>1245</v>
       </c>
       <c r="C695">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D695" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="696" spans="1:4">
@@ -10199,13 +10199,13 @@
         <v>694</v>
       </c>
       <c r="B696">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C696">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D696" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="697" spans="1:4">
@@ -10216,10 +10216,10 @@
         <v>1246</v>
       </c>
       <c r="C697">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D697" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="698" spans="1:4">
@@ -10230,10 +10230,10 @@
         <v>1246</v>
       </c>
       <c r="C698">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D698" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="699" spans="1:4">
@@ -10244,10 +10244,10 @@
         <v>1246</v>
       </c>
       <c r="C699">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D699" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="700" spans="1:4">
@@ -10255,13 +10255,13 @@
         <v>698</v>
       </c>
       <c r="B700">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C700">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D700" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="701" spans="1:4">
@@ -10269,10 +10269,10 @@
         <v>699</v>
       </c>
       <c r="B701">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C701">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D701" t="s">
         <v>5</v>
@@ -10286,10 +10286,10 @@
         <v>1248</v>
       </c>
       <c r="C702">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D702" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="703" spans="1:4">
@@ -10300,10 +10300,10 @@
         <v>1248</v>
       </c>
       <c r="C703">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D703" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="704" spans="1:4">
@@ -10314,10 +10314,10 @@
         <v>1248</v>
       </c>
       <c r="C704">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D704" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="705" spans="1:4">
@@ -10328,7 +10328,7 @@
         <v>1248</v>
       </c>
       <c r="C705">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D705" t="s">
         <v>14</v>
@@ -10342,10 +10342,10 @@
         <v>1248</v>
       </c>
       <c r="C706">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D706" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="707" spans="1:4">
@@ -10356,7 +10356,7 @@
         <v>1248</v>
       </c>
       <c r="C707">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D707" t="s">
         <v>18</v>
@@ -10367,13 +10367,13 @@
         <v>706</v>
       </c>
       <c r="B708">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C708">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D708" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="709" spans="1:4">
@@ -10384,10 +10384,10 @@
         <v>1249</v>
       </c>
       <c r="C709">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D709" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="710" spans="1:4">
@@ -10398,10 +10398,10 @@
         <v>1249</v>
       </c>
       <c r="C710">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D710" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="711" spans="1:4">
@@ -10412,10 +10412,10 @@
         <v>1249</v>
       </c>
       <c r="C711">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D711" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="712" spans="1:4">
@@ -10426,10 +10426,10 @@
         <v>1249</v>
       </c>
       <c r="C712">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D712" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="713" spans="1:4">
@@ -10440,10 +10440,10 @@
         <v>1249</v>
       </c>
       <c r="C713">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D713" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="714" spans="1:4">
@@ -10454,10 +10454,10 @@
         <v>1249</v>
       </c>
       <c r="C714">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D714" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="715" spans="1:4">
@@ -10468,10 +10468,10 @@
         <v>1249</v>
       </c>
       <c r="C715">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D715" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="716" spans="1:4">
@@ -10482,10 +10482,10 @@
         <v>1249</v>
       </c>
       <c r="C716">
+        <v>11</v>
+      </c>
+      <c r="D716" t="s">
         <v>12</v>
-      </c>
-      <c r="D716" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="717" spans="1:4">
@@ -10496,10 +10496,10 @@
         <v>1249</v>
       </c>
       <c r="C717">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D717" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="718" spans="1:4">
@@ -10510,10 +10510,10 @@
         <v>1249</v>
       </c>
       <c r="C718">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D718" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="719" spans="1:4">
@@ -10521,13 +10521,13 @@
         <v>717</v>
       </c>
       <c r="B719">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C719">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D719" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="720" spans="1:4">
@@ -10538,10 +10538,10 @@
         <v>1250</v>
       </c>
       <c r="C720">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D720" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="721" spans="1:5">
@@ -10552,10 +10552,10 @@
         <v>1250</v>
       </c>
       <c r="C721">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D721" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="722" spans="1:5">
@@ -10566,10 +10566,10 @@
         <v>1250</v>
       </c>
       <c r="C722">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D722" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="723" spans="1:5">
@@ -10577,13 +10577,13 @@
         <v>721</v>
       </c>
       <c r="B723">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C723">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D723" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="724" spans="1:5">
@@ -10594,10 +10594,10 @@
         <v>1252</v>
       </c>
       <c r="C724">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D724" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="725" spans="1:5">
@@ -10608,10 +10608,10 @@
         <v>1252</v>
       </c>
       <c r="C725">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D725" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="726" spans="1:5">
@@ -10622,12 +10622,9 @@
         <v>1252</v>
       </c>
       <c r="C726">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D726" t="s">
-        <v>9</v>
-      </c>
-      <c r="E726" t="s">
         <v>8</v>
       </c>
     </row>
@@ -10639,10 +10636,13 @@
         <v>1252</v>
       </c>
       <c r="C727">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D727" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="E727" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="728" spans="1:5">
@@ -10650,13 +10650,13 @@
         <v>726</v>
       </c>
       <c r="B728">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C728">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D728" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="729" spans="1:5">
@@ -10667,10 +10667,10 @@
         <v>1253</v>
       </c>
       <c r="C729">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D729" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="730" spans="1:5">
@@ -10681,10 +10681,10 @@
         <v>1253</v>
       </c>
       <c r="C730">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D730" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="731" spans="1:5">
@@ -10695,10 +10695,10 @@
         <v>1253</v>
       </c>
       <c r="C731">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D731" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="732" spans="1:5">
@@ -10709,10 +10709,10 @@
         <v>1253</v>
       </c>
       <c r="C732">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D732" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="733" spans="1:5">
@@ -10723,10 +10723,10 @@
         <v>1253</v>
       </c>
       <c r="C733">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D733" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="734" spans="1:5">
@@ -10737,10 +10737,10 @@
         <v>1253</v>
       </c>
       <c r="C734">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D734" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="735" spans="1:5">
@@ -10748,13 +10748,13 @@
         <v>733</v>
       </c>
       <c r="B735">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C735">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D735" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="736" spans="1:5">
@@ -10765,10 +10765,10 @@
         <v>1254</v>
       </c>
       <c r="C736">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D736" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="737" spans="1:4">
@@ -10779,10 +10779,10 @@
         <v>1254</v>
       </c>
       <c r="C737">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D737" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="738" spans="1:4">
@@ -10793,10 +10793,10 @@
         <v>1254</v>
       </c>
       <c r="C738">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D738" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="739" spans="1:4">
@@ -10807,7 +10807,7 @@
         <v>1254</v>
       </c>
       <c r="C739">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D739" t="s">
         <v>15</v>
@@ -10821,10 +10821,10 @@
         <v>1254</v>
       </c>
       <c r="C740">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D740" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="741" spans="1:4">
@@ -10835,10 +10835,10 @@
         <v>1254</v>
       </c>
       <c r="C741">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D741" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="742" spans="1:4">
@@ -10849,10 +10849,10 @@
         <v>1254</v>
       </c>
       <c r="C742">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D742" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="743" spans="1:4">
@@ -10863,10 +10863,10 @@
         <v>1254</v>
       </c>
       <c r="C743">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D743" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="744" spans="1:4">
@@ -10877,7 +10877,7 @@
         <v>1254</v>
       </c>
       <c r="C744">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D744" t="s">
         <v>8</v>
@@ -10891,10 +10891,10 @@
         <v>1254</v>
       </c>
       <c r="C745">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D745" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="746" spans="1:4">
@@ -10902,13 +10902,13 @@
         <v>744</v>
       </c>
       <c r="B746">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C746">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D746" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="747" spans="1:4">
@@ -10919,10 +10919,10 @@
         <v>1255</v>
       </c>
       <c r="C747">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D747" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="748" spans="1:4">
@@ -10933,10 +10933,10 @@
         <v>1255</v>
       </c>
       <c r="C748">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D748" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="749" spans="1:4">
@@ -10947,10 +10947,10 @@
         <v>1255</v>
       </c>
       <c r="C749">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D749" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="750" spans="1:4">
@@ -10961,10 +10961,10 @@
         <v>1255</v>
       </c>
       <c r="C750">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D750" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="751" spans="1:4">
@@ -10975,10 +10975,10 @@
         <v>1255</v>
       </c>
       <c r="C751">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D751" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="752" spans="1:4">
@@ -10986,13 +10986,13 @@
         <v>750</v>
       </c>
       <c r="B752">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C752">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D752" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="753" spans="1:4">
@@ -11003,10 +11003,10 @@
         <v>1256</v>
       </c>
       <c r="C753">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D753" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="754" spans="1:4">
@@ -11017,10 +11017,10 @@
         <v>1256</v>
       </c>
       <c r="C754">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D754" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="755" spans="1:4">
@@ -11031,10 +11031,10 @@
         <v>1256</v>
       </c>
       <c r="C755">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D755" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="756" spans="1:4">
@@ -11045,10 +11045,10 @@
         <v>1256</v>
       </c>
       <c r="C756">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D756" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="757" spans="1:4">
@@ -11056,13 +11056,13 @@
         <v>755</v>
       </c>
       <c r="B757">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C757">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D757" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="758" spans="1:4">
@@ -11073,10 +11073,10 @@
         <v>1257</v>
       </c>
       <c r="C758">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D758" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="759" spans="1:4">
@@ -11087,10 +11087,10 @@
         <v>1257</v>
       </c>
       <c r="C759">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D759" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="760" spans="1:4">
@@ -11101,9 +11101,23 @@
         <v>1257</v>
       </c>
       <c r="C760">
+        <v>2</v>
+      </c>
+      <c r="D760" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4">
+      <c r="A761" s="1">
+        <v>759</v>
+      </c>
+      <c r="B761">
+        <v>1257</v>
+      </c>
+      <c r="C761">
         <v>4</v>
       </c>
-      <c r="D760" t="s">
+      <c r="D761" t="s">
         <v>9</v>
       </c>
     </row>
